--- a/Presentation/New_Student_Management/Sources/Spreadsheets/candidate_list.xlsx
+++ b/Presentation/New_Student_Management/Sources/Spreadsheets/candidate_list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Projects\C# Projects\Student_Management\Sources\Spreadsheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Projects\C# Projects\School_Management\Presentation\New_Student_Management\Sources\Spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224361E3-168C-492D-962C-627A334DDD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9676B3D2-2525-41B0-A6A0-706C83231FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{E51BC222-ABB5-406A-BACB-6DFB53F1EC79}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{E51BC222-ABB5-406A-BACB-6DFB53F1EC79}"/>
   </bookViews>
   <sheets>
     <sheet name="Exam Room 1" sheetId="14" state="hidden" r:id="rId1"/>
@@ -55,6 +55,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1149,7 +1152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1415,9 +1418,6 @@
     <xf numFmtId="165" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1448,6 +1448,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1462,33 +1489,6 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1827,99 +1827,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
     </row>
     <row r="2" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="98" t="s">
+      <c r="A2" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
     </row>
     <row r="3" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="99">
+      <c r="A3" s="98">
         <v>3</v>
       </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
     </row>
     <row r="5" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
     </row>
     <row r="6" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="94"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="94"/>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
+      <c r="B6" s="93"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="93"/>
     </row>
     <row r="7" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="94" t="s">
+      <c r="A7" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
     </row>
     <row r="8" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="95" t="s">
+      <c r="A8" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="95"/>
-      <c r="C8" s="95"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="94"/>
+      <c r="D8" s="94"/>
+      <c r="E8" s="94"/>
+      <c r="F8" s="94"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="94"/>
     </row>
     <row r="9" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="96" t="s">
+      <c r="A9" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="96"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
+      <c r="B9" s="95"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="95"/>
+      <c r="E9" s="95"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="95"/>
+      <c r="I9" s="95"/>
     </row>
     <row r="10" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
@@ -2948,102 +2948,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
     </row>
     <row r="2" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="98" t="s">
+      <c r="A2" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
     </row>
     <row r="3" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="99">
+      <c r="A3" s="98">
         <v>3</v>
       </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
     </row>
     <row r="4" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A4" s="103" t="s">
+      <c r="A4" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="102"/>
       <c r="G4" s="31"/>
     </row>
     <row r="5" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A5" s="103" t="s">
+      <c r="A5" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
       <c r="G5" s="31"/>
     </row>
     <row r="6" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="99" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="100"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="100"/>
-      <c r="F6" s="100"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
       <c r="G6" s="30"/>
     </row>
     <row r="7" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A7" s="101" t="s">
+      <c r="A7" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="B7" s="101"/>
-      <c r="C7" s="101"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="101"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="100"/>
     </row>
     <row r="8" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A8" s="102" t="s">
+      <c r="A8" s="101" t="s">
         <v>106</v>
       </c>
-      <c r="B8" s="102"/>
-      <c r="C8" s="102"/>
-      <c r="D8" s="102"/>
-      <c r="E8" s="102"/>
-      <c r="F8" s="102"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="102"/>
-      <c r="I8" s="102"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="101"/>
+      <c r="F8" s="101"/>
+      <c r="G8" s="101"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="101"/>
     </row>
     <row r="9" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
@@ -4015,156 +4015,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="103" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
     </row>
     <row r="2" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="115"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
     </row>
     <row r="3" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="116">
+      <c r="A3" s="106">
         <v>3</v>
       </c>
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116"/>
-      <c r="J3" s="116"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="116"/>
+      <c r="B3" s="106"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="106"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="106"/>
     </row>
     <row r="4" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="117" t="s">
+      <c r="A4" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="117"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="107"/>
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="117" t="s">
+      <c r="A5" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="117"/>
-      <c r="K5" s="117"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
       <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="109" t="s">
+      <c r="A6" s="108" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="109"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="109"/>
-      <c r="E6" s="109"/>
-      <c r="F6" s="109"/>
-      <c r="G6" s="109"/>
-      <c r="H6" s="109"/>
-      <c r="I6" s="109"/>
-      <c r="J6" s="109"/>
-      <c r="K6" s="109"/>
-      <c r="L6" s="109"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="108"/>
+      <c r="L6" s="108"/>
     </row>
     <row r="7" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="109" t="s">
+      <c r="A7" s="108" t="s">
         <v>176</v>
       </c>
-      <c r="B7" s="109"/>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="109"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="109"/>
-      <c r="J7" s="109"/>
-      <c r="K7" s="109"/>
-      <c r="L7" s="109"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="108"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="108"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="108"/>
     </row>
     <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="110" t="s">
+      <c r="A8" s="109" t="s">
         <v>177</v>
       </c>
-      <c r="B8" s="110" t="s">
+      <c r="B8" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="110" t="s">
+      <c r="C8" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="110" t="s">
+      <c r="D8" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="111" t="s">
+      <c r="E8" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="110" t="s">
+      <c r="F8" s="109" t="s">
         <v>178</v>
       </c>
-      <c r="G8" s="112" t="s">
+      <c r="G8" s="111" t="s">
         <v>179</v>
       </c>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="110" t="s">
+      <c r="H8" s="109"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="109"/>
+      <c r="K8" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="L8" s="110" t="s">
+      <c r="L8" s="109" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="110"/>
-      <c r="B9" s="110"/>
-      <c r="C9" s="110"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="111"/>
-      <c r="F9" s="110"/>
+      <c r="A9" s="109"/>
+      <c r="B9" s="109"/>
+      <c r="C9" s="109"/>
+      <c r="D9" s="109"/>
+      <c r="E9" s="110"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="64" t="s">
         <v>180</v>
       </c>
@@ -4177,8 +4177,8 @@
       <c r="J9" s="61" t="s">
         <v>182</v>
       </c>
-      <c r="K9" s="110"/>
-      <c r="L9" s="110"/>
+      <c r="K9" s="109"/>
+      <c r="L9" s="109"/>
     </row>
     <row r="10" spans="1:12" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="62">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="F10" s="67">
         <f ca="1">IF(E10 &lt;&gt; "",YEAR(NOW())-YEAR(E10), "")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" s="90" t="s">
         <v>185</v>
@@ -4211,84 +4211,84 @@
       <c r="K10" s="63" t="s">
         <v>186</v>
       </c>
-      <c r="L10" s="93"/>
+      <c r="L10" s="63"/>
     </row>
     <row r="11" spans="1:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="106"/>
-      <c r="B11" s="106"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="106"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="106"/>
-      <c r="I11" s="106"/>
-      <c r="J11" s="106"/>
-      <c r="K11" s="106"/>
-      <c r="L11" s="106"/>
+      <c r="A11" s="114"/>
+      <c r="B11" s="114"/>
+      <c r="C11" s="114"/>
+      <c r="D11" s="114"/>
+      <c r="E11" s="114"/>
+      <c r="F11" s="114"/>
+      <c r="G11" s="114"/>
+      <c r="H11" s="114"/>
+      <c r="I11" s="114"/>
+      <c r="J11" s="114"/>
+      <c r="K11" s="114"/>
+      <c r="L11" s="114"/>
     </row>
     <row r="12" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28"/>
-      <c r="B12" s="107">
+      <c r="B12" s="115">
         <v>0</v>
       </c>
-      <c r="C12" s="107"/>
+      <c r="C12" s="115"/>
       <c r="D12" s="57"/>
       <c r="E12" s="65"/>
       <c r="F12" s="89"/>
-      <c r="G12" s="108" t="s">
+      <c r="G12" s="116" t="s">
         <v>187</v>
       </c>
-      <c r="H12" s="108"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="108"/>
-      <c r="K12" s="108"/>
-      <c r="L12" s="108"/>
+      <c r="H12" s="116"/>
+      <c r="I12" s="116"/>
+      <c r="J12" s="116"/>
+      <c r="K12" s="116"/>
+      <c r="L12" s="116"/>
     </row>
     <row r="13" spans="1:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26"/>
-      <c r="B13" s="107">
+      <c r="B13" s="115">
         <v>0</v>
       </c>
-      <c r="C13" s="107"/>
-      <c r="G13" s="108" t="str">
+      <c r="C13" s="115"/>
+      <c r="G13" s="116" t="str">
         <f>_xlfn.CONCAT("   ដុនបូស្កូប៉ោយប៉ែត ថ្ងៃទី","១៣","   ខែ","កញ្ញា","    ឆ្នាំ","២០២៤")</f>
         <v xml:space="preserve">   ដុនបូស្កូប៉ោយប៉ែត ថ្ងៃទី១៣   ខែកញ្ញា    ឆ្នាំ២០២៤</v>
       </c>
-      <c r="H13" s="108"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="108"/>
-      <c r="K13" s="108"/>
-      <c r="L13" s="108"/>
+      <c r="H13" s="116"/>
+      <c r="I13" s="116"/>
+      <c r="J13" s="116"/>
+      <c r="K13" s="116"/>
+      <c r="L13" s="116"/>
     </row>
     <row r="14" spans="1:12" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="8"/>
       <c r="G14" s="74"/>
-      <c r="H14" s="104" t="s">
+      <c r="H14" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="I14" s="104"/>
-      <c r="J14" s="104"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="104"/>
+      <c r="I14" s="112"/>
+      <c r="J14" s="112"/>
+      <c r="K14" s="112"/>
+      <c r="L14" s="112"/>
     </row>
     <row r="15" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="28"/>
-      <c r="B15" s="105" t="s">
+      <c r="B15" s="113" t="s">
         <v>190</v>
       </c>
-      <c r="C15" s="105"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="105"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="113"/>
     </row>
     <row r="16" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="28"/>
-      <c r="B16" s="104" t="s">
+      <c r="B16" s="112" t="s">
         <v>191</v>
       </c>
-      <c r="C16" s="104"/>
-      <c r="D16" s="104"/>
-      <c r="E16" s="104"/>
+      <c r="C16" s="112"/>
+      <c r="D16" s="112"/>
+      <c r="E16" s="112"/>
       <c r="F16" s="59"/>
       <c r="G16" s="59"/>
       <c r="H16" s="59"/>
@@ -4528,11 +4528,14 @@
     <sortCondition ref="B10"/>
   </sortState>
   <mergeCells count="24">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="G13:L13"/>
     <mergeCell ref="A6:L6"/>
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A8:A9"/>
@@ -4544,14 +4547,11 @@
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="L8:L9"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G13:L13"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -4583,156 +4583,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="103" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
     </row>
     <row r="2" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="115"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
     </row>
     <row r="3" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="116">
+      <c r="A3" s="106">
         <v>3</v>
       </c>
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116"/>
-      <c r="J3" s="116"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="116"/>
+      <c r="B3" s="106"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="106"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="106"/>
     </row>
     <row r="4" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="117" t="s">
+      <c r="A4" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="117"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="107"/>
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="117" t="s">
+      <c r="A5" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="117"/>
-      <c r="K5" s="117"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
       <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="109" t="s">
+      <c r="A6" s="108" t="s">
         <v>192</v>
       </c>
-      <c r="B6" s="109"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="109"/>
-      <c r="E6" s="109"/>
-      <c r="F6" s="109"/>
-      <c r="G6" s="109"/>
-      <c r="H6" s="109"/>
-      <c r="I6" s="109"/>
-      <c r="J6" s="109"/>
-      <c r="K6" s="109"/>
-      <c r="L6" s="109"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="108"/>
+      <c r="L6" s="108"/>
     </row>
     <row r="7" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="109" t="s">
+      <c r="A7" s="108" t="s">
         <v>176</v>
       </c>
-      <c r="B7" s="109"/>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="109"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="109"/>
-      <c r="J7" s="109"/>
-      <c r="K7" s="109"/>
-      <c r="L7" s="109"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="108"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="108"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="108"/>
     </row>
     <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="110" t="s">
+      <c r="A8" s="109" t="s">
         <v>177</v>
       </c>
-      <c r="B8" s="110" t="s">
+      <c r="B8" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="110" t="s">
+      <c r="C8" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="110" t="s">
+      <c r="D8" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="111" t="s">
+      <c r="E8" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="110" t="s">
+      <c r="F8" s="109" t="s">
         <v>178</v>
       </c>
-      <c r="G8" s="112" t="s">
+      <c r="G8" s="111" t="s">
         <v>179</v>
       </c>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="110" t="s">
+      <c r="H8" s="109"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="109"/>
+      <c r="K8" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="L8" s="110" t="s">
+      <c r="L8" s="109" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="110"/>
-      <c r="B9" s="110"/>
-      <c r="C9" s="110"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="111"/>
-      <c r="F9" s="110"/>
+      <c r="A9" s="109"/>
+      <c r="B9" s="109"/>
+      <c r="C9" s="109"/>
+      <c r="D9" s="109"/>
+      <c r="E9" s="110"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="70" t="s">
         <v>180</v>
       </c>
@@ -4745,10 +4745,10 @@
       <c r="J9" s="71" t="s">
         <v>182</v>
       </c>
-      <c r="K9" s="110"/>
-      <c r="L9" s="110"/>
-    </row>
-    <row r="10" spans="1:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K9" s="109"/>
+      <c r="L9" s="109"/>
+    </row>
+    <row r="10" spans="1:12" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="62">
         <v>1</v>
       </c>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F10" s="67">
         <f ca="1">IF(E10 &lt;&gt; "",YEAR(NOW())-YEAR(E10), "")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" s="90" t="s">
         <v>185</v>
@@ -4779,83 +4779,83 @@
       <c r="K10" s="63" t="s">
         <v>186</v>
       </c>
-      <c r="L10" s="93"/>
+      <c r="L10" s="63"/>
     </row>
     <row r="11" spans="1:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="106"/>
-      <c r="B11" s="106"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="106"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="106"/>
-      <c r="I11" s="106"/>
-      <c r="J11" s="106"/>
-      <c r="K11" s="106"/>
-      <c r="L11" s="106"/>
+      <c r="A11" s="114"/>
+      <c r="B11" s="114"/>
+      <c r="C11" s="114"/>
+      <c r="D11" s="114"/>
+      <c r="E11" s="114"/>
+      <c r="F11" s="114"/>
+      <c r="G11" s="114"/>
+      <c r="H11" s="114"/>
+      <c r="I11" s="114"/>
+      <c r="J11" s="114"/>
+      <c r="K11" s="114"/>
+      <c r="L11" s="114"/>
     </row>
     <row r="12" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28"/>
-      <c r="B12" s="107">
+      <c r="B12" s="115">
         <v>0</v>
       </c>
-      <c r="C12" s="107"/>
+      <c r="C12" s="115"/>
       <c r="D12" s="57"/>
       <c r="E12" s="65"/>
       <c r="F12" s="57"/>
-      <c r="G12" s="108" t="s">
+      <c r="G12" s="116" t="s">
         <v>187</v>
       </c>
-      <c r="H12" s="108"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="108"/>
-      <c r="K12" s="108"/>
-      <c r="L12" s="108"/>
+      <c r="H12" s="116"/>
+      <c r="I12" s="116"/>
+      <c r="J12" s="116"/>
+      <c r="K12" s="116"/>
+      <c r="L12" s="116"/>
     </row>
     <row r="13" spans="1:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26"/>
-      <c r="B13" s="107">
+      <c r="B13" s="115">
         <v>0</v>
       </c>
-      <c r="C13" s="107"/>
-      <c r="G13" s="108" t="s">
+      <c r="C13" s="115"/>
+      <c r="G13" s="116" t="s">
         <v>188</v>
       </c>
-      <c r="H13" s="108"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="108"/>
-      <c r="K13" s="108"/>
-      <c r="L13" s="108"/>
+      <c r="H13" s="116"/>
+      <c r="I13" s="116"/>
+      <c r="J13" s="116"/>
+      <c r="K13" s="116"/>
+      <c r="L13" s="116"/>
     </row>
     <row r="14" spans="1:12" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="72"/>
-      <c r="H14" s="104" t="s">
+      <c r="H14" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="I14" s="104"/>
-      <c r="J14" s="104"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="104"/>
+      <c r="I14" s="112"/>
+      <c r="J14" s="112"/>
+      <c r="K14" s="112"/>
+      <c r="L14" s="112"/>
     </row>
     <row r="15" spans="1:12" s="72" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="28"/>
-      <c r="B15" s="105" t="s">
+      <c r="B15" s="113" t="s">
         <v>190</v>
       </c>
-      <c r="C15" s="105"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="105"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="113"/>
       <c r="I15"/>
     </row>
     <row r="16" spans="1:12" s="72" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="28"/>
-      <c r="B16" s="104" t="s">
+      <c r="B16" s="112" t="s">
         <v>191</v>
       </c>
-      <c r="C16" s="104"/>
-      <c r="D16" s="104"/>
-      <c r="E16" s="104"/>
+      <c r="C16" s="112"/>
+      <c r="D16" s="112"/>
+      <c r="E16" s="112"/>
       <c r="F16" s="69"/>
       <c r="G16" s="69"/>
       <c r="H16" s="69"/>
@@ -5182,12 +5182,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="G13:L13"/>
+    <mergeCell ref="H14:L14"/>
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
@@ -5198,14 +5200,12 @@
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="L8:L9"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G13:L13"/>
-    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5236,156 +5236,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="103" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
     </row>
     <row r="2" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="115"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
     </row>
     <row r="3" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="116">
+      <c r="A3" s="106">
         <v>3</v>
       </c>
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116"/>
-      <c r="J3" s="116"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="116"/>
+      <c r="B3" s="106"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="106"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="106"/>
     </row>
     <row r="4" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="117" t="s">
+      <c r="A4" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="117"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="107"/>
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="117" t="s">
+      <c r="A5" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="117"/>
-      <c r="K5" s="117"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
       <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="109" t="s">
+      <c r="A6" s="108" t="s">
         <v>193</v>
       </c>
-      <c r="B6" s="109"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="109"/>
-      <c r="E6" s="109"/>
-      <c r="F6" s="109"/>
-      <c r="G6" s="109"/>
-      <c r="H6" s="109"/>
-      <c r="I6" s="109"/>
-      <c r="J6" s="109"/>
-      <c r="K6" s="109"/>
-      <c r="L6" s="109"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="108"/>
+      <c r="L6" s="108"/>
     </row>
     <row r="7" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="109" t="s">
+      <c r="A7" s="108" t="s">
         <v>176</v>
       </c>
-      <c r="B7" s="109"/>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="109"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="109"/>
-      <c r="J7" s="109"/>
-      <c r="K7" s="109"/>
-      <c r="L7" s="109"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="108"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="108"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="108"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="108"/>
     </row>
     <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="110" t="s">
+      <c r="A8" s="109" t="s">
         <v>177</v>
       </c>
-      <c r="B8" s="110" t="s">
+      <c r="B8" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="110" t="s">
+      <c r="C8" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="110" t="s">
+      <c r="D8" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="111" t="s">
+      <c r="E8" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="110" t="s">
+      <c r="F8" s="109" t="s">
         <v>178</v>
       </c>
-      <c r="G8" s="112" t="s">
+      <c r="G8" s="111" t="s">
         <v>179</v>
       </c>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="110" t="s">
+      <c r="H8" s="109"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="109"/>
+      <c r="K8" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="L8" s="110" t="s">
+      <c r="L8" s="109" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="110"/>
-      <c r="B9" s="110"/>
-      <c r="C9" s="110"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="111"/>
-      <c r="F9" s="110"/>
+      <c r="A9" s="109"/>
+      <c r="B9" s="109"/>
+      <c r="C9" s="109"/>
+      <c r="D9" s="109"/>
+      <c r="E9" s="110"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="70" t="s">
         <v>180</v>
       </c>
@@ -5398,10 +5398,10 @@
       <c r="J9" s="71" t="s">
         <v>182</v>
       </c>
-      <c r="K9" s="110"/>
-      <c r="L9" s="110"/>
-    </row>
-    <row r="10" spans="1:12" ht="16.899999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K9" s="109"/>
+      <c r="L9" s="109"/>
+    </row>
+    <row r="10" spans="1:12" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="62">
         <v>1</v>
       </c>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="F10" s="67">
         <f ca="1">IF(E10 &lt;&gt; "",YEAR(NOW())-YEAR(E10), "")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" s="90" t="s">
         <v>185</v>
@@ -5432,83 +5432,83 @@
       <c r="K10" s="63" t="s">
         <v>186</v>
       </c>
-      <c r="L10" s="93"/>
+      <c r="L10" s="63"/>
     </row>
     <row r="11" spans="1:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="106"/>
-      <c r="B11" s="106"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="106"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="106"/>
-      <c r="I11" s="106"/>
-      <c r="J11" s="106"/>
-      <c r="K11" s="106"/>
-      <c r="L11" s="106"/>
+      <c r="A11" s="114"/>
+      <c r="B11" s="114"/>
+      <c r="C11" s="114"/>
+      <c r="D11" s="114"/>
+      <c r="E11" s="114"/>
+      <c r="F11" s="114"/>
+      <c r="G11" s="114"/>
+      <c r="H11" s="114"/>
+      <c r="I11" s="114"/>
+      <c r="J11" s="114"/>
+      <c r="K11" s="114"/>
+      <c r="L11" s="114"/>
     </row>
     <row r="12" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28"/>
-      <c r="B12" s="107">
+      <c r="B12" s="115">
         <v>0</v>
       </c>
-      <c r="C12" s="107"/>
+      <c r="C12" s="115"/>
       <c r="D12" s="57"/>
       <c r="E12" s="65"/>
       <c r="F12" s="57"/>
-      <c r="G12" s="108" t="s">
+      <c r="G12" s="116" t="s">
         <v>187</v>
       </c>
-      <c r="H12" s="108"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="108"/>
-      <c r="K12" s="108"/>
-      <c r="L12" s="108"/>
+      <c r="H12" s="116"/>
+      <c r="I12" s="116"/>
+      <c r="J12" s="116"/>
+      <c r="K12" s="116"/>
+      <c r="L12" s="116"/>
     </row>
     <row r="13" spans="1:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26"/>
-      <c r="B13" s="107">
+      <c r="B13" s="115">
         <v>0</v>
       </c>
-      <c r="C13" s="107"/>
-      <c r="G13" s="108" t="s">
+      <c r="C13" s="115"/>
+      <c r="G13" s="116" t="s">
         <v>188</v>
       </c>
-      <c r="H13" s="108"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="108"/>
-      <c r="K13" s="108"/>
-      <c r="L13" s="108"/>
+      <c r="H13" s="116"/>
+      <c r="I13" s="116"/>
+      <c r="J13" s="116"/>
+      <c r="K13" s="116"/>
+      <c r="L13" s="116"/>
     </row>
     <row r="14" spans="1:12" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="72"/>
-      <c r="H14" s="104" t="s">
+      <c r="H14" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="I14" s="104"/>
-      <c r="J14" s="104"/>
-      <c r="K14" s="104"/>
-      <c r="L14" s="104"/>
+      <c r="I14" s="112"/>
+      <c r="J14" s="112"/>
+      <c r="K14" s="112"/>
+      <c r="L14" s="112"/>
     </row>
     <row r="15" spans="1:12" s="72" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="28"/>
-      <c r="B15" s="105" t="s">
+      <c r="B15" s="113" t="s">
         <v>190</v>
       </c>
-      <c r="C15" s="105"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="105"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="113"/>
       <c r="I15"/>
     </row>
     <row r="16" spans="1:12" s="72" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="28"/>
-      <c r="B16" s="104" t="s">
+      <c r="B16" s="112" t="s">
         <v>191</v>
       </c>
-      <c r="C16" s="104"/>
-      <c r="D16" s="104"/>
-      <c r="E16" s="104"/>
+      <c r="C16" s="112"/>
+      <c r="D16" s="112"/>
+      <c r="E16" s="112"/>
       <c r="F16" s="69"/>
       <c r="G16" s="69"/>
       <c r="H16" s="69"/>
@@ -5835,12 +5835,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="G13:L13"/>
+    <mergeCell ref="H14:L14"/>
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
@@ -5851,14 +5853,12 @@
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="L8:L9"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G13:L13"/>
-    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5890,98 +5890,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
     </row>
     <row r="2" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="95" t="s">
+      <c r="A2" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="118"/>
-      <c r="C2" s="118"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118"/>
-      <c r="F2" s="118"/>
-      <c r="G2" s="118"/>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="118"/>
-      <c r="K2" s="118"/>
-      <c r="L2" s="118"/>
-      <c r="M2" s="118"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
     </row>
     <row r="3" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="116">
+      <c r="A3" s="106">
         <v>3</v>
       </c>
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116"/>
-      <c r="J3" s="116"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="116"/>
-      <c r="M3" s="116"/>
+      <c r="B3" s="106"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="106"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="106"/>
+      <c r="M3" s="106"/>
     </row>
     <row r="5" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A5" s="103" t="s">
+      <c r="A5" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
       <c r="G5" s="31"/>
     </row>
     <row r="6" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A6" s="103" t="s">
+      <c r="A6" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="103"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
       <c r="G6" s="31"/>
     </row>
     <row r="7" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="D7" s="1"/>
-      <c r="E7" s="101" t="s">
+      <c r="E7" s="100" t="s">
         <v>194</v>
       </c>
-      <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="101"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="100"/>
       <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="D8" s="1"/>
-      <c r="E8" s="101" t="s">
+      <c r="E8" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="101"/>
-      <c r="G8" s="101"/>
-      <c r="H8" s="101"/>
-      <c r="I8" s="101"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="100"/>
+      <c r="H8" s="100"/>
+      <c r="I8" s="100"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/Presentation/New_Student_Management/Sources/Spreadsheets/candidate_list.xlsx
+++ b/Presentation/New_Student_Management/Sources/Spreadsheets/candidate_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Projects\C# Projects\School_Management\Presentation\New_Student_Management\Sources\Spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9676B3D2-2525-41B0-A6A0-706C83231FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2D4361-31BA-4B2C-A72E-5335EC3CED4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{E51BC222-ABB5-406A-BACB-6DFB53F1EC79}"/>
   </bookViews>
@@ -16,9 +16,7 @@
     <sheet name="Exam Room 1" sheetId="14" state="hidden" r:id="rId1"/>
     <sheet name="Exam Room 2" sheetId="13" state="hidden" r:id="rId2"/>
     <sheet name="Computer" sheetId="7" r:id="rId3"/>
-    <sheet name="Electrical" sheetId="16" r:id="rId4"/>
-    <sheet name="CNC" sheetId="17" r:id="rId5"/>
-    <sheet name="Result" sheetId="9" state="hidden" r:id="rId6"/>
+    <sheet name="Result" sheetId="9" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Attendant_Condition" localSheetId="1">'Exam Room 2'!#REF!</definedName>
@@ -29,18 +27,13 @@
     <definedName name="Attendant_Total_Score" localSheetId="1">'Exam Room 2'!#REF!</definedName>
     <definedName name="Computer_Genders" localSheetId="0">'Exam Room 1'!#REF!</definedName>
     <definedName name="Computer_Numbers" localSheetId="0">'Exam Room 1'!#REF!</definedName>
-    <definedName name="GregorianReportDate">Computer!$G$13,Electrical!$G$13,CNC!$G$13</definedName>
-    <definedName name="LunarReportDate">Computer!$G$12,CNC!$G$12,Electrical!$G$12</definedName>
-    <definedName name="StudyYear">Computer!$A$7,Electrical!$A$7,CNC!$A$7</definedName>
-    <definedName name="SummaryCell" localSheetId="4">CNC!$A$11</definedName>
+    <definedName name="GregorianReportDate">Computer!$G$13</definedName>
+    <definedName name="LunarReportDate">Computer!$G$12</definedName>
+    <definedName name="StudyYear">Computer!$A$7</definedName>
     <definedName name="SummaryCell" localSheetId="2">Computer!$A$11</definedName>
-    <definedName name="SummaryCell" localSheetId="3">Electrical!$A$11</definedName>
-    <definedName name="TotalFemaleStudents" localSheetId="4">CNC!$B$13</definedName>
+    <definedName name="TitleSkill">Computer!$A$6</definedName>
     <definedName name="TotalFemaleStudents" localSheetId="2">Computer!$B$13</definedName>
-    <definedName name="TotalFemaleStudents" localSheetId="3">Electrical!$B$13</definedName>
-    <definedName name="TotalStudents" localSheetId="4">CNC!$B$12</definedName>
     <definedName name="TotalStudents" localSheetId="2">Computer!$B$12</definedName>
-    <definedName name="TotalStudents" localSheetId="3">Electrical!$B$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -86,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="229">
   <si>
     <t>ព្រះរាជាណាចក្រកម្ពុជា</t>
   </si>
@@ -652,9 +645,6 @@
     <t xml:space="preserve"> ថ្ងៃ សុក្រ  ១១កើត  ខែភទ្របទ  ឆ្នាំរោង ឆស័ក ព.ស.២៥៦៨</t>
   </si>
   <si>
-    <t xml:space="preserve">   ដុនបូស្កូប៉ោយប៉ែត ថ្ងៃទី១៣   ខែកញ្ញា    ឆ្នាំ២០២៤</t>
-  </si>
-  <si>
     <t>អ្នកធ្វើតារាង</t>
   </si>
   <si>
@@ -662,12 +652,6 @@
   </si>
   <si>
     <t>នាយកវិទ្យាល័យ</t>
-  </si>
-  <si>
-    <t>បញ្ជីរាយនាមសិស្សចូលរៀនបច្ចេកទេស កម្រិត១ ផ្នែកអគ្គិសនី</t>
-  </si>
-  <si>
-    <t>បញ្ជីរាយនាមសិស្សចូលរៀនបច្ចេកទេស កម្រិត១ ផ្នែកមេកានិចស៊ីអិនស៊ី</t>
   </si>
   <si>
     <t>បញ្ជីរាយនាមសិស្សចូលរៀនឆ្នាំទី១ ទាំង ៣ ផ្នែក</t>
@@ -1152,7 +1136,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1345,24 +1329,6 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1448,6 +1414,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1462,33 +1455,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1827,99 +1793,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
     </row>
     <row r="2" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
     </row>
     <row r="3" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="98">
+      <c r="A3" s="92">
         <v>3</v>
       </c>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
     </row>
     <row r="5" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="93"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
     </row>
     <row r="6" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="93" t="s">
+      <c r="A6" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="93"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
+      <c r="B6" s="87"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
     </row>
     <row r="7" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="93" t="s">
+      <c r="A7" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="93"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="93"/>
-      <c r="F7" s="93"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
     </row>
     <row r="8" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="94" t="s">
+      <c r="A8" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
+      <c r="B8" s="88"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="88"/>
     </row>
     <row r="9" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="95" t="s">
+      <c r="A9" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="95"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="95"/>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
+      <c r="B9" s="89"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="89"/>
+      <c r="E9" s="89"/>
+      <c r="F9" s="89"/>
+      <c r="G9" s="89"/>
+      <c r="H9" s="89"/>
+      <c r="I9" s="89"/>
     </row>
     <row r="10" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
@@ -2016,7 +1982,7 @@
       <c r="D13" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="75">
+      <c r="E13" s="69">
         <v>40071</v>
       </c>
       <c r="F13" s="45" t="s">
@@ -2948,102 +2914,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
     </row>
     <row r="2" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
     </row>
     <row r="3" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="98">
+      <c r="A3" s="92">
         <v>3</v>
       </c>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
     </row>
     <row r="4" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="102"/>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="102"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
       <c r="G4" s="31"/>
     </row>
     <row r="5" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
       <c r="G5" s="31"/>
     </row>
     <row r="6" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="93" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="99"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="99"/>
+      <c r="B6" s="93"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="93"/>
       <c r="G6" s="30"/>
     </row>
     <row r="7" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A7" s="100" t="s">
+      <c r="A7" s="94" t="s">
         <v>105</v>
       </c>
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="100"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="100"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="100"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
     </row>
     <row r="8" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="B8" s="101"/>
-      <c r="C8" s="101"/>
-      <c r="D8" s="101"/>
-      <c r="E8" s="101"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="101"/>
-      <c r="H8" s="101"/>
-      <c r="I8" s="101"/>
+      <c r="B8" s="95"/>
+      <c r="C8" s="95"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="95"/>
+      <c r="I8" s="95"/>
     </row>
     <row r="9" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
@@ -3456,7 +3422,7 @@
       <c r="D24" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="75">
+      <c r="E24" s="69">
         <v>40074</v>
       </c>
       <c r="F24" s="42" t="s">
@@ -3782,7 +3748,7 @@
       <c r="D36" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E36" s="75">
+      <c r="E36" s="69">
         <v>39714</v>
       </c>
       <c r="F36" s="42" t="s">
@@ -3810,7 +3776,7 @@
       <c r="D37" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E37" s="76">
+      <c r="E37" s="70">
         <v>38727</v>
       </c>
       <c r="F37" s="42" t="s">
@@ -3836,7 +3802,7 @@
       <c r="D38" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E38" s="76">
+      <c r="E38" s="70">
         <v>39248</v>
       </c>
       <c r="F38" s="42" t="s">
@@ -3862,7 +3828,7 @@
       <c r="D39" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E39" s="76">
+      <c r="E39" s="70">
         <v>39158</v>
       </c>
       <c r="F39" s="42" t="s">
@@ -4015,156 +3981,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="106" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
     </row>
     <row r="2" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="108"/>
+      <c r="L2" s="108"/>
     </row>
     <row r="3" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="106">
+      <c r="A3" s="109">
         <v>3</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="109"/>
+      <c r="K3" s="109"/>
+      <c r="L3" s="109"/>
     </row>
     <row r="4" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="107" t="s">
+      <c r="A4" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="107"/>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="107"/>
+      <c r="B4" s="110"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="107" t="s">
+      <c r="A5" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="107"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="107"/>
-      <c r="I5" s="107"/>
-      <c r="J5" s="107"/>
-      <c r="K5" s="107"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="110"/>
       <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="108" t="s">
+      <c r="A6" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="108"/>
-      <c r="L6" s="108"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="102"/>
+      <c r="L6" s="102"/>
     </row>
     <row r="7" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="108" t="s">
+      <c r="A7" s="102" t="s">
         <v>176</v>
       </c>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="108"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="108"/>
-      <c r="K7" s="108"/>
-      <c r="L7" s="108"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="102"/>
     </row>
     <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="109" t="s">
+      <c r="A8" s="103" t="s">
         <v>177</v>
       </c>
-      <c r="B8" s="109" t="s">
+      <c r="B8" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="109" t="s">
+      <c r="C8" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="109" t="s">
+      <c r="D8" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="110" t="s">
+      <c r="E8" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="109" t="s">
+      <c r="F8" s="103" t="s">
         <v>178</v>
       </c>
-      <c r="G8" s="111" t="s">
+      <c r="G8" s="105" t="s">
         <v>179</v>
       </c>
-      <c r="H8" s="109"/>
-      <c r="I8" s="109"/>
-      <c r="J8" s="109"/>
-      <c r="K8" s="109" t="s">
+      <c r="H8" s="103"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="103"/>
+      <c r="K8" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="L8" s="109" t="s">
+      <c r="L8" s="103" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="109"/>
-      <c r="B9" s="109"/>
-      <c r="C9" s="109"/>
-      <c r="D9" s="109"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="109"/>
+      <c r="A9" s="103"/>
+      <c r="B9" s="103"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="103"/>
       <c r="G9" s="64" t="s">
         <v>180</v>
       </c>
@@ -4177,8 +4143,8 @@
       <c r="J9" s="61" t="s">
         <v>182</v>
       </c>
-      <c r="K9" s="109"/>
-      <c r="L9" s="109"/>
+      <c r="K9" s="103"/>
+      <c r="L9" s="103"/>
     </row>
     <row r="10" spans="1:12" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="62">
@@ -4193,17 +4159,17 @@
       <c r="D10" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="92">
+      <c r="E10" s="86">
         <v>40134</v>
       </c>
       <c r="F10" s="67">
         <f ca="1">IF(E10 &lt;&gt; "",YEAR(NOW())-YEAR(E10), "")</f>
         <v>17</v>
       </c>
-      <c r="G10" s="90" t="s">
+      <c r="G10" s="84" t="s">
         <v>185</v>
       </c>
-      <c r="H10" s="91">
+      <c r="H10" s="85">
         <v>45852</v>
       </c>
       <c r="I10" s="62"/>
@@ -4214,81 +4180,81 @@
       <c r="L10" s="63"/>
     </row>
     <row r="11" spans="1:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="114"/>
-      <c r="B11" s="114"/>
-      <c r="C11" s="114"/>
-      <c r="D11" s="114"/>
-      <c r="E11" s="114"/>
-      <c r="F11" s="114"/>
-      <c r="G11" s="114"/>
-      <c r="H11" s="114"/>
-      <c r="I11" s="114"/>
-      <c r="J11" s="114"/>
-      <c r="K11" s="114"/>
-      <c r="L11" s="114"/>
+      <c r="A11" s="99"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="99"/>
+      <c r="K11" s="99"/>
+      <c r="L11" s="99"/>
     </row>
     <row r="12" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28"/>
-      <c r="B12" s="115">
+      <c r="B12" s="100">
         <v>0</v>
       </c>
-      <c r="C12" s="115"/>
+      <c r="C12" s="100"/>
       <c r="D12" s="57"/>
       <c r="E12" s="65"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="116" t="s">
+      <c r="F12" s="83"/>
+      <c r="G12" s="101" t="s">
         <v>187</v>
       </c>
-      <c r="H12" s="116"/>
-      <c r="I12" s="116"/>
-      <c r="J12" s="116"/>
-      <c r="K12" s="116"/>
-      <c r="L12" s="116"/>
+      <c r="H12" s="101"/>
+      <c r="I12" s="101"/>
+      <c r="J12" s="101"/>
+      <c r="K12" s="101"/>
+      <c r="L12" s="101"/>
     </row>
     <row r="13" spans="1:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26"/>
-      <c r="B13" s="115">
+      <c r="B13" s="100">
         <v>0</v>
       </c>
-      <c r="C13" s="115"/>
-      <c r="G13" s="116" t="str">
+      <c r="C13" s="100"/>
+      <c r="G13" s="101" t="str">
         <f>_xlfn.CONCAT("   ដុនបូស្កូប៉ោយប៉ែត ថ្ងៃទី","១៣","   ខែ","កញ្ញា","    ឆ្នាំ","២០២៤")</f>
         <v xml:space="preserve">   ដុនបូស្កូប៉ោយប៉ែត ថ្ងៃទី១៣   ខែកញ្ញា    ឆ្នាំ២០២៤</v>
       </c>
-      <c r="H13" s="116"/>
-      <c r="I13" s="116"/>
-      <c r="J13" s="116"/>
-      <c r="K13" s="116"/>
-      <c r="L13" s="116"/>
+      <c r="H13" s="101"/>
+      <c r="I13" s="101"/>
+      <c r="J13" s="101"/>
+      <c r="K13" s="101"/>
+      <c r="L13" s="101"/>
     </row>
     <row r="14" spans="1:12" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="8"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="112" t="s">
-        <v>189</v>
-      </c>
-      <c r="I14" s="112"/>
-      <c r="J14" s="112"/>
-      <c r="K14" s="112"/>
-      <c r="L14" s="112"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="97" t="s">
+        <v>188</v>
+      </c>
+      <c r="I14" s="97"/>
+      <c r="J14" s="97"/>
+      <c r="K14" s="97"/>
+      <c r="L14" s="97"/>
     </row>
     <row r="15" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="28"/>
-      <c r="B15" s="113" t="s">
-        <v>190</v>
-      </c>
-      <c r="C15" s="113"/>
-      <c r="D15" s="113"/>
-      <c r="E15" s="113"/>
+      <c r="B15" s="98" t="s">
+        <v>189</v>
+      </c>
+      <c r="C15" s="98"/>
+      <c r="D15" s="98"/>
+      <c r="E15" s="98"/>
     </row>
     <row r="16" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="28"/>
-      <c r="B16" s="112" t="s">
-        <v>191</v>
-      </c>
-      <c r="C16" s="112"/>
-      <c r="D16" s="112"/>
-      <c r="E16" s="112"/>
+      <c r="B16" s="97" t="s">
+        <v>190</v>
+      </c>
+      <c r="C16" s="97"/>
+      <c r="D16" s="97"/>
+      <c r="E16" s="97"/>
       <c r="F16" s="59"/>
       <c r="G16" s="59"/>
       <c r="H16" s="59"/>
@@ -4528,14 +4494,11 @@
     <sortCondition ref="B10"/>
   </sortState>
   <mergeCells count="24">
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G13:L13"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:L6"/>
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A8:A9"/>
@@ -4547,11 +4510,14 @@
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="G13:L13"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -4561,1312 +4527,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1BF5CB9-CC25-44C8-A3D9-032F03C8590D}">
-  <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
-  </sheetPr>
-  <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.85546875" style="27" customWidth="1"/>
-    <col min="2" max="2" width="10" style="60" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="72" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" style="72" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="66" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" style="72" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" style="72" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="72" customWidth="1"/>
-    <col min="9" max="9" width="7.85546875" customWidth="1"/>
-    <col min="10" max="10" width="7.85546875" style="72" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" style="72" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" style="72" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-    </row>
-    <row r="2" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="104" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-    </row>
-    <row r="3" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="106">
-        <v>3</v>
-      </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-    </row>
-    <row r="4" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="107" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="107"/>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="6"/>
-    </row>
-    <row r="5" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="107" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="107"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="107"/>
-      <c r="I5" s="107"/>
-      <c r="J5" s="107"/>
-      <c r="K5" s="107"/>
-      <c r="L5" s="6"/>
-    </row>
-    <row r="6" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="108" t="s">
-        <v>192</v>
-      </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="108"/>
-      <c r="L6" s="108"/>
-    </row>
-    <row r="7" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="108" t="s">
-        <v>176</v>
-      </c>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="108"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="108"/>
-      <c r="K7" s="108"/>
-      <c r="L7" s="108"/>
-    </row>
-    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="109" t="s">
-        <v>177</v>
-      </c>
-      <c r="B8" s="109" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="109" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="109" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="110" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="109" t="s">
-        <v>178</v>
-      </c>
-      <c r="G8" s="111" t="s">
-        <v>179</v>
-      </c>
-      <c r="H8" s="109"/>
-      <c r="I8" s="109"/>
-      <c r="J8" s="109"/>
-      <c r="K8" s="109" t="s">
-        <v>12</v>
-      </c>
-      <c r="L8" s="109" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="109"/>
-      <c r="B9" s="109"/>
-      <c r="C9" s="109"/>
-      <c r="D9" s="109"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="109"/>
-      <c r="G9" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="H9" s="71" t="s">
-        <v>181</v>
-      </c>
-      <c r="I9" s="71" t="s">
-        <v>7</v>
-      </c>
-      <c r="J9" s="71" t="s">
-        <v>182</v>
-      </c>
-      <c r="K9" s="109"/>
-      <c r="L9" s="109"/>
-    </row>
-    <row r="10" spans="1:12" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="62">
-        <v>1</v>
-      </c>
-      <c r="B10" s="63" t="s">
-        <v>183</v>
-      </c>
-      <c r="C10" s="63" t="s">
-        <v>184</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="92">
-        <v>40134</v>
-      </c>
-      <c r="F10" s="67">
-        <f ca="1">IF(E10 &lt;&gt; "",YEAR(NOW())-YEAR(E10), "")</f>
-        <v>17</v>
-      </c>
-      <c r="G10" s="90" t="s">
-        <v>185</v>
-      </c>
-      <c r="H10" s="91">
-        <v>45852</v>
-      </c>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="63" t="s">
-        <v>186</v>
-      </c>
-      <c r="L10" s="63"/>
-    </row>
-    <row r="11" spans="1:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="114"/>
-      <c r="B11" s="114"/>
-      <c r="C11" s="114"/>
-      <c r="D11" s="114"/>
-      <c r="E11" s="114"/>
-      <c r="F11" s="114"/>
-      <c r="G11" s="114"/>
-      <c r="H11" s="114"/>
-      <c r="I11" s="114"/>
-      <c r="J11" s="114"/>
-      <c r="K11" s="114"/>
-      <c r="L11" s="114"/>
-    </row>
-    <row r="12" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28"/>
-      <c r="B12" s="115">
-        <v>0</v>
-      </c>
-      <c r="C12" s="115"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="65"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="116" t="s">
-        <v>187</v>
-      </c>
-      <c r="H12" s="116"/>
-      <c r="I12" s="116"/>
-      <c r="J12" s="116"/>
-      <c r="K12" s="116"/>
-      <c r="L12" s="116"/>
-    </row>
-    <row r="13" spans="1:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="115">
-        <v>0</v>
-      </c>
-      <c r="C13" s="115"/>
-      <c r="G13" s="116" t="s">
-        <v>188</v>
-      </c>
-      <c r="H13" s="116"/>
-      <c r="I13" s="116"/>
-      <c r="J13" s="116"/>
-      <c r="K13" s="116"/>
-      <c r="L13" s="116"/>
-    </row>
-    <row r="14" spans="1:12" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="72"/>
-      <c r="H14" s="112" t="s">
-        <v>189</v>
-      </c>
-      <c r="I14" s="112"/>
-      <c r="J14" s="112"/>
-      <c r="K14" s="112"/>
-      <c r="L14" s="112"/>
-    </row>
-    <row r="15" spans="1:12" s="72" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="113" t="s">
-        <v>190</v>
-      </c>
-      <c r="C15" s="113"/>
-      <c r="D15" s="113"/>
-      <c r="E15" s="113"/>
-      <c r="I15"/>
-    </row>
-    <row r="16" spans="1:12" s="72" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28"/>
-      <c r="B16" s="112" t="s">
-        <v>191</v>
-      </c>
-      <c r="C16" s="112"/>
-      <c r="D16" s="112"/>
-      <c r="E16" s="112"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
-      <c r="I16"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="73"/>
-    </row>
-    <row r="17" spans="1:9" s="72" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="68"/>
-      <c r="I17"/>
-    </row>
-    <row r="18" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28"/>
-      <c r="B18" s="7"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="I18"/>
-    </row>
-    <row r="19" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="27"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="I19"/>
-    </row>
-    <row r="20" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="27"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="I20"/>
-    </row>
-    <row r="21" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="27"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="I21"/>
-    </row>
-    <row r="22" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="27"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="I22"/>
-    </row>
-    <row r="23" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="27"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="I23"/>
-    </row>
-    <row r="24" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="27"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="I24"/>
-    </row>
-    <row r="25" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="27"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="I25"/>
-    </row>
-    <row r="26" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="27"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="I26"/>
-    </row>
-    <row r="27" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="27"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="I27"/>
-    </row>
-    <row r="28" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="27"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="I28"/>
-    </row>
-    <row r="29" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="27"/>
-      <c r="E29" s="66"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="I29"/>
-    </row>
-    <row r="30" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="27"/>
-      <c r="E30" s="66"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="I30"/>
-    </row>
-    <row r="31" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="27"/>
-      <c r="E31" s="66"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="I31"/>
-    </row>
-    <row r="32" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="27"/>
-      <c r="E32" s="66"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="I32"/>
-    </row>
-    <row r="33" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="27"/>
-      <c r="E33" s="66"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="I33"/>
-    </row>
-    <row r="34" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="27"/>
-      <c r="E34" s="66"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="I34"/>
-    </row>
-    <row r="35" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="27"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="I35"/>
-    </row>
-    <row r="36" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="27"/>
-      <c r="E36" s="66"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="I36"/>
-    </row>
-    <row r="37" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="27"/>
-      <c r="E37" s="66"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="I37"/>
-    </row>
-    <row r="38" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="27"/>
-      <c r="E38" s="66"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="I38"/>
-    </row>
-    <row r="39" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="27"/>
-      <c r="E39" s="66"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="I39"/>
-    </row>
-    <row r="40" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="27"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="I40"/>
-    </row>
-    <row r="41" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="27"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="I41"/>
-    </row>
-    <row r="42" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="27"/>
-      <c r="E42" s="66"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="I42"/>
-    </row>
-    <row r="43" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="27"/>
-      <c r="E43" s="66"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="I43"/>
-    </row>
-    <row r="44" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="27"/>
-      <c r="E44" s="66"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="I44"/>
-    </row>
-    <row r="45" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="27"/>
-      <c r="E45" s="66"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="I45"/>
-    </row>
-    <row r="46" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="27"/>
-      <c r="E46" s="66"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="I46"/>
-    </row>
-    <row r="47" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="27"/>
-      <c r="E47" s="66"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="I47"/>
-    </row>
-    <row r="48" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="27"/>
-      <c r="E48" s="66"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="I48"/>
-    </row>
-    <row r="49" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="27"/>
-      <c r="E49" s="66"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="I49"/>
-    </row>
-    <row r="50" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="27"/>
-      <c r="E50" s="66"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="I50"/>
-    </row>
-    <row r="51" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="27"/>
-      <c r="E51" s="66"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18"/>
-      <c r="I51"/>
-    </row>
-    <row r="52" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="27"/>
-      <c r="E52" s="66"/>
-      <c r="F52" s="18"/>
-      <c r="G52" s="18"/>
-      <c r="I52"/>
-    </row>
-    <row r="53" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="27"/>
-      <c r="E53" s="66"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
-      <c r="I53"/>
-    </row>
-    <row r="54" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="27"/>
-      <c r="E54" s="66"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="27"/>
-      <c r="E55" s="66"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="I55"/>
-    </row>
-    <row r="56" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="27"/>
-      <c r="E56" s="66"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="I56"/>
-    </row>
-    <row r="57" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="27"/>
-      <c r="E57" s="66"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="18"/>
-      <c r="I57"/>
-    </row>
-    <row r="58" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="27"/>
-      <c r="E58" s="66"/>
-      <c r="F58" s="18"/>
-      <c r="G58" s="18"/>
-      <c r="I58"/>
-    </row>
-    <row r="59" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="27"/>
-      <c r="E59" s="66"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="I59"/>
-    </row>
-    <row r="60" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="27"/>
-      <c r="E60" s="66"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="18"/>
-      <c r="I60"/>
-    </row>
-    <row r="61" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="27"/>
-      <c r="E61" s="66"/>
-      <c r="F61" s="18"/>
-      <c r="G61" s="18"/>
-      <c r="I61"/>
-    </row>
-  </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G13:L13"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18132D55-5839-49C5-89C7-E461A8A22EBD}">
-  <sheetPr>
-    <tabColor rgb="FFFFC000"/>
-  </sheetPr>
-  <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.85546875" style="27" customWidth="1"/>
-    <col min="2" max="2" width="10" style="60" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="72" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" style="72" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="66" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" style="72" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" style="72" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="72" customWidth="1"/>
-    <col min="9" max="9" width="7.85546875" customWidth="1"/>
-    <col min="10" max="10" width="7.85546875" style="72" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" style="72" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" style="72" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-    </row>
-    <row r="2" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="104" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-    </row>
-    <row r="3" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="106">
-        <v>3</v>
-      </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-    </row>
-    <row r="4" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="107" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="107"/>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="6"/>
-    </row>
-    <row r="5" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="107" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="107"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="107"/>
-      <c r="I5" s="107"/>
-      <c r="J5" s="107"/>
-      <c r="K5" s="107"/>
-      <c r="L5" s="6"/>
-    </row>
-    <row r="6" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="108" t="s">
-        <v>193</v>
-      </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="108"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="108"/>
-      <c r="L6" s="108"/>
-    </row>
-    <row r="7" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="108" t="s">
-        <v>176</v>
-      </c>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="108"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="108"/>
-      <c r="K7" s="108"/>
-      <c r="L7" s="108"/>
-    </row>
-    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="109" t="s">
-        <v>177</v>
-      </c>
-      <c r="B8" s="109" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="109" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="109" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="110" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="109" t="s">
-        <v>178</v>
-      </c>
-      <c r="G8" s="111" t="s">
-        <v>179</v>
-      </c>
-      <c r="H8" s="109"/>
-      <c r="I8" s="109"/>
-      <c r="J8" s="109"/>
-      <c r="K8" s="109" t="s">
-        <v>12</v>
-      </c>
-      <c r="L8" s="109" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="109"/>
-      <c r="B9" s="109"/>
-      <c r="C9" s="109"/>
-      <c r="D9" s="109"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="109"/>
-      <c r="G9" s="70" t="s">
-        <v>180</v>
-      </c>
-      <c r="H9" s="71" t="s">
-        <v>181</v>
-      </c>
-      <c r="I9" s="71" t="s">
-        <v>7</v>
-      </c>
-      <c r="J9" s="71" t="s">
-        <v>182</v>
-      </c>
-      <c r="K9" s="109"/>
-      <c r="L9" s="109"/>
-    </row>
-    <row r="10" spans="1:12" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="62">
-        <v>1</v>
-      </c>
-      <c r="B10" s="63" t="s">
-        <v>183</v>
-      </c>
-      <c r="C10" s="63" t="s">
-        <v>184</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="92">
-        <v>40134</v>
-      </c>
-      <c r="F10" s="67">
-        <f ca="1">IF(E10 &lt;&gt; "",YEAR(NOW())-YEAR(E10), "")</f>
-        <v>17</v>
-      </c>
-      <c r="G10" s="90" t="s">
-        <v>185</v>
-      </c>
-      <c r="H10" s="91">
-        <v>45852</v>
-      </c>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="63" t="s">
-        <v>186</v>
-      </c>
-      <c r="L10" s="63"/>
-    </row>
-    <row r="11" spans="1:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="114"/>
-      <c r="B11" s="114"/>
-      <c r="C11" s="114"/>
-      <c r="D11" s="114"/>
-      <c r="E11" s="114"/>
-      <c r="F11" s="114"/>
-      <c r="G11" s="114"/>
-      <c r="H11" s="114"/>
-      <c r="I11" s="114"/>
-      <c r="J11" s="114"/>
-      <c r="K11" s="114"/>
-      <c r="L11" s="114"/>
-    </row>
-    <row r="12" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28"/>
-      <c r="B12" s="115">
-        <v>0</v>
-      </c>
-      <c r="C12" s="115"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="65"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="116" t="s">
-        <v>187</v>
-      </c>
-      <c r="H12" s="116"/>
-      <c r="I12" s="116"/>
-      <c r="J12" s="116"/>
-      <c r="K12" s="116"/>
-      <c r="L12" s="116"/>
-    </row>
-    <row r="13" spans="1:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="115">
-        <v>0</v>
-      </c>
-      <c r="C13" s="115"/>
-      <c r="G13" s="116" t="s">
-        <v>188</v>
-      </c>
-      <c r="H13" s="116"/>
-      <c r="I13" s="116"/>
-      <c r="J13" s="116"/>
-      <c r="K13" s="116"/>
-      <c r="L13" s="116"/>
-    </row>
-    <row r="14" spans="1:12" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="72"/>
-      <c r="H14" s="112" t="s">
-        <v>189</v>
-      </c>
-      <c r="I14" s="112"/>
-      <c r="J14" s="112"/>
-      <c r="K14" s="112"/>
-      <c r="L14" s="112"/>
-    </row>
-    <row r="15" spans="1:12" s="72" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="113" t="s">
-        <v>190</v>
-      </c>
-      <c r="C15" s="113"/>
-      <c r="D15" s="113"/>
-      <c r="E15" s="113"/>
-      <c r="I15"/>
-    </row>
-    <row r="16" spans="1:12" s="72" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28"/>
-      <c r="B16" s="112" t="s">
-        <v>191</v>
-      </c>
-      <c r="C16" s="112"/>
-      <c r="D16" s="112"/>
-      <c r="E16" s="112"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
-      <c r="I16"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="73"/>
-    </row>
-    <row r="17" spans="1:9" s="72" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="68"/>
-      <c r="I17"/>
-    </row>
-    <row r="18" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28"/>
-      <c r="B18" s="7"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="I18"/>
-    </row>
-    <row r="19" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="27"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="I19"/>
-    </row>
-    <row r="20" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="27"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="I20"/>
-    </row>
-    <row r="21" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="27"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="I21"/>
-    </row>
-    <row r="22" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="27"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="I22"/>
-    </row>
-    <row r="23" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="27"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="I23"/>
-    </row>
-    <row r="24" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="27"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="I24"/>
-    </row>
-    <row r="25" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="27"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="I25"/>
-    </row>
-    <row r="26" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="27"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="I26"/>
-    </row>
-    <row r="27" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="27"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="I27"/>
-    </row>
-    <row r="28" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="27"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="I28"/>
-    </row>
-    <row r="29" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="27"/>
-      <c r="E29" s="66"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="I29"/>
-    </row>
-    <row r="30" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="27"/>
-      <c r="E30" s="66"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="I30"/>
-    </row>
-    <row r="31" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="27"/>
-      <c r="E31" s="66"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="I31"/>
-    </row>
-    <row r="32" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="27"/>
-      <c r="E32" s="66"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="I32"/>
-    </row>
-    <row r="33" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="27"/>
-      <c r="E33" s="66"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="I33"/>
-    </row>
-    <row r="34" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="27"/>
-      <c r="E34" s="66"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="I34"/>
-    </row>
-    <row r="35" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="27"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="I35"/>
-    </row>
-    <row r="36" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="27"/>
-      <c r="E36" s="66"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="I36"/>
-    </row>
-    <row r="37" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="27"/>
-      <c r="E37" s="66"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="I37"/>
-    </row>
-    <row r="38" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="27"/>
-      <c r="E38" s="66"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="I38"/>
-    </row>
-    <row r="39" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="27"/>
-      <c r="E39" s="66"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="I39"/>
-    </row>
-    <row r="40" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="27"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="I40"/>
-    </row>
-    <row r="41" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="27"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="I41"/>
-    </row>
-    <row r="42" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="27"/>
-      <c r="E42" s="66"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="I42"/>
-    </row>
-    <row r="43" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="27"/>
-      <c r="E43" s="66"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="I43"/>
-    </row>
-    <row r="44" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="27"/>
-      <c r="E44" s="66"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="I44"/>
-    </row>
-    <row r="45" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="27"/>
-      <c r="E45" s="66"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="I45"/>
-    </row>
-    <row r="46" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="27"/>
-      <c r="E46" s="66"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="I46"/>
-    </row>
-    <row r="47" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="27"/>
-      <c r="E47" s="66"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="I47"/>
-    </row>
-    <row r="48" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="27"/>
-      <c r="E48" s="66"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="I48"/>
-    </row>
-    <row r="49" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="27"/>
-      <c r="E49" s="66"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="I49"/>
-    </row>
-    <row r="50" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="27"/>
-      <c r="E50" s="66"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="I50"/>
-    </row>
-    <row r="51" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="27"/>
-      <c r="E51" s="66"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18"/>
-      <c r="I51"/>
-    </row>
-    <row r="52" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="27"/>
-      <c r="E52" s="66"/>
-      <c r="F52" s="18"/>
-      <c r="G52" s="18"/>
-      <c r="I52"/>
-    </row>
-    <row r="53" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="27"/>
-      <c r="E53" s="66"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
-      <c r="I53"/>
-    </row>
-    <row r="54" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="27"/>
-      <c r="E54" s="66"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="27"/>
-      <c r="E55" s="66"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="I55"/>
-    </row>
-    <row r="56" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="27"/>
-      <c r="E56" s="66"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="I56"/>
-    </row>
-    <row r="57" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="27"/>
-      <c r="E57" s="66"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="18"/>
-      <c r="I57"/>
-    </row>
-    <row r="58" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="27"/>
-      <c r="E58" s="66"/>
-      <c r="F58" s="18"/>
-      <c r="G58" s="18"/>
-      <c r="I58"/>
-    </row>
-    <row r="59" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="27"/>
-      <c r="E59" s="66"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="I59"/>
-    </row>
-    <row r="60" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="27"/>
-      <c r="E60" s="66"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="18"/>
-      <c r="I60"/>
-    </row>
-    <row r="61" spans="1:9" s="72" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="27"/>
-      <c r="E61" s="66"/>
-      <c r="F61" s="18"/>
-      <c r="G61" s="18"/>
-      <c r="I61"/>
-    </row>
-  </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="G13:L13"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4132A3-0CD4-49B4-B546-F8D903D52472}">
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FFFF0000"/>
@@ -5890,98 +4550,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
     </row>
     <row r="2" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="117"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="117"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="111"/>
+      <c r="J2" s="111"/>
+      <c r="K2" s="111"/>
+      <c r="L2" s="111"/>
+      <c r="M2" s="111"/>
     </row>
     <row r="3" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="106">
+      <c r="A3" s="109">
         <v>3</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="109"/>
+      <c r="K3" s="109"/>
+      <c r="L3" s="109"/>
+      <c r="M3" s="109"/>
     </row>
     <row r="5" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
       <c r="G5" s="31"/>
     </row>
     <row r="6" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A6" s="102" t="s">
+      <c r="A6" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
+      <c r="B6" s="96"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="96"/>
       <c r="G6" s="31"/>
     </row>
     <row r="7" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="D7" s="1"/>
-      <c r="E7" s="100" t="s">
-        <v>194</v>
-      </c>
-      <c r="F7" s="100"/>
-      <c r="G7" s="100"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="100"/>
+      <c r="E7" s="94" t="s">
+        <v>191</v>
+      </c>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
       <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="D8" s="1"/>
-      <c r="E8" s="100" t="s">
+      <c r="E8" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="100"/>
-      <c r="G8" s="100"/>
-      <c r="H8" s="100"/>
-      <c r="I8" s="100"/>
+      <c r="F8" s="94"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="94"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6004,1272 +4664,1272 @@
         <v>12</v>
       </c>
       <c r="G9" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="J9" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="K9" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="L9" s="16" t="s">
         <v>197</v>
-      </c>
-      <c r="J9" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>200</v>
       </c>
       <c r="M9" s="16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="78">
+    <row r="10" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="72">
         <f>IF(B10&lt;&gt;"",1,"")</f>
         <v>1</v>
       </c>
-      <c r="B10" s="79" t="s">
+      <c r="B10" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="79" t="s">
+      <c r="D10" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="80">
+      <c r="E10" s="74">
         <v>39724</v>
       </c>
-      <c r="F10" s="81" t="s">
+      <c r="F10" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="82">
+      <c r="G10" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="76">
         <v>65</v>
       </c>
-      <c r="I10" s="82">
+      <c r="I10" s="76">
         <v>40</v>
       </c>
-      <c r="J10" s="82">
+      <c r="J10" s="76">
         <f t="shared" ref="J10:J41" si="0">IF(OR(H10&lt;&gt;"",I10&lt;&gt;""),SUM(H10:I10),"")</f>
         <v>105</v>
       </c>
-      <c r="K10" s="82">
+      <c r="K10" s="76">
         <f t="shared" ref="K10:K41" si="1">IF(J10="","",RANK(J10,$J$10:$J$86))</f>
         <v>50</v>
       </c>
-      <c r="L10" s="81" t="str">
+      <c r="L10" s="75" t="str">
         <f t="shared" ref="L10:L41" si="2">IF(K10="","",IF(J10&gt;=100,"ជាប់","ធ្លាក់"))</f>
         <v>ជាប់</v>
       </c>
-      <c r="M10" s="83"/>
+      <c r="M10" s="77"/>
       <c r="N10"/>
     </row>
-    <row r="11" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="78">
+    <row r="11" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="72">
         <f t="shared" ref="A11:A42" ca="1" si="3">IF(B11="", "", INDIRECT("A" &amp; ROW(A10)) + 1)</f>
         <v>2</v>
       </c>
-      <c r="B11" s="79" t="s">
+      <c r="B11" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="79" t="s">
+      <c r="C11" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="80">
+      <c r="D11" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="74">
         <v>38779</v>
       </c>
-      <c r="F11" s="81" t="s">
+      <c r="F11" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="82">
+      <c r="G11" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="76">
         <v>60</v>
       </c>
-      <c r="I11" s="82">
+      <c r="I11" s="76">
         <v>68</v>
       </c>
-      <c r="J11" s="82">
+      <c r="J11" s="76">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="K11" s="82">
+      <c r="K11" s="76">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L11" s="81" t="str">
+      <c r="L11" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M11" s="83"/>
+      <c r="M11" s="77"/>
       <c r="N11"/>
     </row>
-    <row r="12" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="78">
+    <row r="12" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>3</v>
       </c>
-      <c r="B12" s="79" t="s">
+      <c r="B12" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="79" t="s">
+      <c r="C12" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="80">
+      <c r="D12" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="74">
         <v>38779</v>
       </c>
-      <c r="F12" s="81" t="s">
+      <c r="F12" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="82">
+      <c r="G12" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="76">
         <v>60</v>
       </c>
-      <c r="I12" s="82">
+      <c r="I12" s="76">
         <v>70</v>
       </c>
-      <c r="J12" s="82">
+      <c r="J12" s="76">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="K12" s="82">
+      <c r="K12" s="76">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="L12" s="81" t="str">
+      <c r="L12" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M12" s="83"/>
+      <c r="M12" s="77"/>
       <c r="N12"/>
     </row>
-    <row r="13" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="78">
+    <row r="13" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>4</v>
       </c>
-      <c r="B13" s="79" t="s">
+      <c r="B13" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="79" t="s">
+      <c r="C13" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="80">
+      <c r="D13" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="74">
         <v>40338</v>
       </c>
-      <c r="F13" s="81" t="s">
+      <c r="F13" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="G13" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="82">
+      <c r="G13" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="76">
         <v>75</v>
       </c>
-      <c r="I13" s="82">
+      <c r="I13" s="76">
         <v>0</v>
       </c>
-      <c r="J13" s="82">
+      <c r="J13" s="76">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="K13" s="82">
+      <c r="K13" s="76">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
-      <c r="L13" s="81" t="str">
+      <c r="L13" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ធ្លាក់</v>
       </c>
-      <c r="M13" s="83"/>
+      <c r="M13" s="77"/>
       <c r="N13"/>
     </row>
-    <row r="14" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="78">
+    <row r="14" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>5</v>
       </c>
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="73" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="79" t="s">
+      <c r="C14" s="73" t="s">
         <v>118</v>
       </c>
-      <c r="D14" s="79" t="s">
+      <c r="D14" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="80">
+      <c r="E14" s="74">
         <v>39838</v>
       </c>
-      <c r="F14" s="81" t="s">
+      <c r="F14" s="75" t="s">
         <v>119</v>
       </c>
-      <c r="G14" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="82">
+      <c r="G14" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="76">
         <v>65</v>
       </c>
-      <c r="I14" s="82">
+      <c r="I14" s="76">
         <v>54</v>
       </c>
-      <c r="J14" s="82">
+      <c r="J14" s="76">
         <f t="shared" si="0"/>
         <v>119</v>
       </c>
-      <c r="K14" s="82">
+      <c r="K14" s="76">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="L14" s="81" t="str">
+      <c r="L14" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M14" s="83"/>
+      <c r="M14" s="77"/>
       <c r="N14"/>
     </row>
-    <row r="15" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="78">
+    <row r="15" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>6</v>
       </c>
-      <c r="B15" s="79" t="s">
+      <c r="B15" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="79" t="s">
+      <c r="C15" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="79" t="s">
+      <c r="D15" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="80">
+      <c r="E15" s="74">
         <v>39507</v>
       </c>
-      <c r="F15" s="81" t="s">
+      <c r="F15" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="G15" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="82">
+      <c r="G15" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="76">
         <v>70</v>
       </c>
-      <c r="I15" s="82">
+      <c r="I15" s="76">
         <v>54</v>
       </c>
-      <c r="J15" s="82">
+      <c r="J15" s="76">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
-      <c r="K15" s="82">
+      <c r="K15" s="76">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="L15" s="81" t="str">
+      <c r="L15" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M15" s="83" t="s">
+      <c r="M15" s="77" t="s">
         <v>42</v>
       </c>
       <c r="N15"/>
     </row>
-    <row r="16" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="78">
+    <row r="16" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>7</v>
       </c>
-      <c r="B16" s="79" t="s">
+      <c r="B16" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="79" t="s">
+      <c r="C16" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="79" t="s">
+      <c r="D16" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="80">
+      <c r="E16" s="74">
         <v>40143</v>
       </c>
-      <c r="F16" s="81" t="s">
+      <c r="F16" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="82">
+      <c r="G16" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="76">
         <v>75</v>
       </c>
-      <c r="I16" s="82">
+      <c r="I16" s="76">
         <v>70</v>
       </c>
-      <c r="J16" s="82">
+      <c r="J16" s="76">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
-      <c r="K16" s="82">
+      <c r="K16" s="76">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="L16" s="81" t="str">
+      <c r="L16" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M16" s="83"/>
+      <c r="M16" s="77"/>
       <c r="N16"/>
     </row>
-    <row r="17" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="78">
+    <row r="17" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>8</v>
       </c>
-      <c r="B17" s="79" t="s">
+      <c r="B17" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="79" t="s">
+      <c r="C17" s="73" t="s">
         <v>85</v>
       </c>
-      <c r="D17" s="79" t="s">
+      <c r="D17" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="80">
+      <c r="E17" s="74">
         <v>39782</v>
       </c>
-      <c r="F17" s="81" t="s">
+      <c r="F17" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="G17" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="82">
+      <c r="G17" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="76">
         <v>70</v>
       </c>
-      <c r="I17" s="82">
+      <c r="I17" s="76">
         <v>40</v>
       </c>
-      <c r="J17" s="82">
+      <c r="J17" s="76">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-      <c r="K17" s="82">
+      <c r="K17" s="76">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="L17" s="81" t="str">
+      <c r="L17" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M17" s="83"/>
+      <c r="M17" s="77"/>
       <c r="N17"/>
     </row>
-    <row r="18" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="78">
+    <row r="18" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>9</v>
       </c>
-      <c r="B18" s="79" t="s">
-        <v>201</v>
-      </c>
-      <c r="C18" s="79" t="s">
-        <v>202</v>
-      </c>
-      <c r="D18" s="79" t="s">
+      <c r="B18" s="73" t="s">
+        <v>198</v>
+      </c>
+      <c r="C18" s="73" t="s">
+        <v>199</v>
+      </c>
+      <c r="D18" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="80">
+      <c r="E18" s="74">
         <v>39810</v>
       </c>
-      <c r="F18" s="81" t="s">
-        <v>203</v>
-      </c>
-      <c r="G18" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="82">
+      <c r="F18" s="75" t="s">
+        <v>200</v>
+      </c>
+      <c r="G18" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="76">
         <v>65</v>
       </c>
-      <c r="I18" s="82">
+      <c r="I18" s="76">
         <v>43</v>
       </c>
-      <c r="J18" s="82">
+      <c r="J18" s="76">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
-      <c r="K18" s="82">
+      <c r="K18" s="76">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="L18" s="81" t="str">
+      <c r="L18" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M18" s="83" t="s">
-        <v>204</v>
+      <c r="M18" s="77" t="s">
+        <v>201</v>
       </c>
       <c r="N18"/>
     </row>
-    <row r="19" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="78">
+    <row r="19" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>10</v>
       </c>
-      <c r="B19" s="79" t="s">
+      <c r="B19" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="79" t="s">
+      <c r="C19" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="79" t="s">
+      <c r="D19" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="80">
+      <c r="E19" s="74">
         <v>40030</v>
       </c>
-      <c r="F19" s="81" t="s">
+      <c r="F19" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="G19" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="82">
+      <c r="G19" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="76">
         <v>60</v>
       </c>
-      <c r="I19" s="82">
+      <c r="I19" s="76">
         <v>69</v>
       </c>
-      <c r="J19" s="82">
+      <c r="J19" s="76">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
-      <c r="K19" s="82">
+      <c r="K19" s="76">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="L19" s="81" t="str">
+      <c r="L19" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M19" s="83"/>
+      <c r="M19" s="77"/>
       <c r="N19"/>
     </row>
-    <row r="20" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="78">
+    <row r="20" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>11</v>
       </c>
-      <c r="B20" s="79" t="s">
+      <c r="B20" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="C20" s="79" t="s">
+      <c r="C20" s="73" t="s">
         <v>134</v>
       </c>
-      <c r="D20" s="79" t="s">
+      <c r="D20" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="80">
+      <c r="E20" s="74">
         <v>39886</v>
       </c>
-      <c r="F20" s="84" t="s">
+      <c r="F20" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="G20" s="84" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="82">
+      <c r="G20" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="76">
         <v>65</v>
       </c>
-      <c r="I20" s="82">
+      <c r="I20" s="76">
         <v>52</v>
       </c>
-      <c r="J20" s="82">
+      <c r="J20" s="76">
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="K20" s="82">
+      <c r="K20" s="76">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="L20" s="81" t="str">
+      <c r="L20" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M20" s="83"/>
+      <c r="M20" s="77"/>
       <c r="N20"/>
     </row>
-    <row r="21" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="78">
+    <row r="21" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>12</v>
       </c>
-      <c r="B21" s="79" t="s">
+      <c r="B21" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="79" t="s">
+      <c r="C21" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="80">
+      <c r="D21" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="74">
         <v>39790</v>
       </c>
-      <c r="F21" s="81" t="s">
+      <c r="F21" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H21" s="82">
+      <c r="G21" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="76">
         <v>65</v>
       </c>
-      <c r="I21" s="82">
+      <c r="I21" s="76">
         <v>36</v>
       </c>
-      <c r="J21" s="82">
+      <c r="J21" s="76">
         <f t="shared" si="0"/>
         <v>101</v>
       </c>
-      <c r="K21" s="82">
+      <c r="K21" s="76">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="L21" s="81" t="str">
+      <c r="L21" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M21" s="83"/>
+      <c r="M21" s="77"/>
       <c r="N21"/>
     </row>
-    <row r="22" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="78">
+    <row r="22" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>13</v>
       </c>
-      <c r="B22" s="79" t="s">
+      <c r="B22" s="73" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="79" t="s">
+      <c r="C22" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="80">
+      <c r="D22" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="74">
         <v>39821</v>
       </c>
-      <c r="F22" s="81" t="s">
+      <c r="F22" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="G22" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="82">
+      <c r="G22" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="76">
         <v>60</v>
       </c>
-      <c r="I22" s="82">
+      <c r="I22" s="76">
         <v>48</v>
       </c>
-      <c r="J22" s="82">
+      <c r="J22" s="76">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
-      <c r="K22" s="82">
+      <c r="K22" s="76">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="L22" s="81" t="str">
+      <c r="L22" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M22" s="83"/>
+      <c r="M22" s="77"/>
       <c r="N22"/>
     </row>
-    <row r="23" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="78">
+    <row r="23" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>14</v>
       </c>
-      <c r="B23" s="79" t="s">
+      <c r="B23" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="79" t="s">
+      <c r="C23" s="73" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="80">
+      <c r="D23" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="74">
         <v>39902</v>
       </c>
-      <c r="F23" s="81" t="s">
+      <c r="F23" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="G23" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="82">
+      <c r="G23" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="76">
         <v>55</v>
       </c>
-      <c r="I23" s="82">
+      <c r="I23" s="76">
         <v>56</v>
       </c>
-      <c r="J23" s="82">
+      <c r="J23" s="76">
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
-      <c r="K23" s="82">
+      <c r="K23" s="76">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="L23" s="81" t="str">
+      <c r="L23" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M23" s="83"/>
+      <c r="M23" s="77"/>
       <c r="N23"/>
     </row>
-    <row r="24" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="78">
+    <row r="24" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>15</v>
       </c>
-      <c r="B24" s="79" t="s">
+      <c r="B24" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="79" t="s">
+      <c r="C24" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="79" t="s">
+      <c r="D24" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="80">
+      <c r="E24" s="74">
         <v>39900</v>
       </c>
-      <c r="F24" s="81" t="s">
+      <c r="F24" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="G24" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="82">
+      <c r="G24" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="76">
         <v>65</v>
       </c>
-      <c r="I24" s="82">
+      <c r="I24" s="76">
         <v>59</v>
       </c>
-      <c r="J24" s="82">
+      <c r="J24" s="76">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
-      <c r="K24" s="82">
+      <c r="K24" s="76">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="L24" s="81" t="str">
+      <c r="L24" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M24" s="83"/>
+      <c r="M24" s="77"/>
       <c r="N24"/>
     </row>
-    <row r="25" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="78">
+    <row r="25" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>16</v>
       </c>
-      <c r="B25" s="79" t="s">
+      <c r="B25" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="79" t="s">
+      <c r="C25" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="79" t="s">
+      <c r="D25" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="80">
+      <c r="E25" s="74">
         <v>39971</v>
       </c>
-      <c r="F25" s="81" t="s">
+      <c r="F25" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="G25" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" s="85">
+      <c r="G25" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="79">
         <v>70</v>
       </c>
-      <c r="I25" s="82">
+      <c r="I25" s="76">
         <v>42</v>
       </c>
-      <c r="J25" s="82">
+      <c r="J25" s="76">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
-      <c r="K25" s="82">
+      <c r="K25" s="76">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="L25" s="81" t="str">
+      <c r="L25" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M25" s="83"/>
+      <c r="M25" s="77"/>
       <c r="N25"/>
     </row>
-    <row r="26" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="78">
+    <row r="26" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>17</v>
       </c>
-      <c r="B26" s="79" t="s">
+      <c r="B26" s="73" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="79" t="s">
+      <c r="C26" s="73" t="s">
         <v>87</v>
       </c>
-      <c r="D26" s="79" t="s">
+      <c r="D26" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E26" s="80">
+      <c r="E26" s="74">
         <v>38737</v>
       </c>
-      <c r="F26" s="81" t="s">
+      <c r="F26" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="G26" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H26" s="82">
+      <c r="G26" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="76">
         <v>60</v>
       </c>
-      <c r="I26" s="82">
+      <c r="I26" s="76">
         <v>33</v>
       </c>
-      <c r="J26" s="82">
+      <c r="J26" s="76">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="K26" s="82">
+      <c r="K26" s="76">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="L26" s="81" t="str">
+      <c r="L26" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ធ្លាក់</v>
       </c>
-      <c r="M26" s="83"/>
+      <c r="M26" s="77"/>
       <c r="N26"/>
     </row>
-    <row r="27" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="78">
+    <row r="27" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>18</v>
       </c>
-      <c r="B27" s="79" t="s">
+      <c r="B27" s="73" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="79" t="s">
+      <c r="C27" s="73" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="79" t="s">
+      <c r="D27" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E27" s="80">
+      <c r="E27" s="74">
         <v>39561</v>
       </c>
-      <c r="F27" s="81" t="s">
+      <c r="F27" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="86">
+      <c r="G27" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="80">
         <v>70</v>
       </c>
-      <c r="I27" s="82">
+      <c r="I27" s="76">
         <v>44</v>
       </c>
-      <c r="J27" s="82">
+      <c r="J27" s="76">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
-      <c r="K27" s="82">
+      <c r="K27" s="76">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="L27" s="81" t="str">
+      <c r="L27" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M27" s="83"/>
+      <c r="M27" s="77"/>
       <c r="N27"/>
     </row>
-    <row r="28" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="78">
+    <row r="28" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>19</v>
       </c>
-      <c r="B28" s="79" t="s">
+      <c r="B28" s="73" t="s">
         <v>174</v>
       </c>
-      <c r="C28" s="79" t="s">
-        <v>205</v>
-      </c>
-      <c r="D28" s="79" t="s">
+      <c r="C28" s="73" t="s">
+        <v>202</v>
+      </c>
+      <c r="D28" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="80">
+      <c r="E28" s="74">
         <v>39550</v>
       </c>
-      <c r="F28" s="81" t="s">
+      <c r="F28" s="75" t="s">
         <v>109</v>
       </c>
-      <c r="G28" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="82">
+      <c r="G28" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="76">
         <v>60</v>
       </c>
-      <c r="I28" s="82">
+      <c r="I28" s="76">
         <v>29</v>
       </c>
-      <c r="J28" s="82">
+      <c r="J28" s="76">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="K28" s="82">
+      <c r="K28" s="76">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="L28" s="81" t="str">
+      <c r="L28" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ធ្លាក់</v>
       </c>
-      <c r="M28" s="83"/>
+      <c r="M28" s="77"/>
       <c r="N28"/>
     </row>
-    <row r="29" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="78">
+    <row r="29" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>20</v>
       </c>
-      <c r="B29" s="79" t="s">
+      <c r="B29" s="73" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="79" t="s">
+      <c r="C29" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="79" t="s">
+      <c r="D29" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E29" s="80">
+      <c r="E29" s="74">
         <v>39266</v>
       </c>
-      <c r="F29" s="81" t="s">
+      <c r="F29" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="82">
+      <c r="G29" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="76">
         <v>70</v>
       </c>
-      <c r="I29" s="82">
+      <c r="I29" s="76">
         <v>62</v>
       </c>
-      <c r="J29" s="82">
+      <c r="J29" s="76">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-      <c r="K29" s="82">
+      <c r="K29" s="76">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L29" s="81" t="str">
+      <c r="L29" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M29" s="83" t="s">
+      <c r="M29" s="77" t="s">
         <v>42</v>
       </c>
       <c r="N29"/>
     </row>
-    <row r="30" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="78">
+    <row r="30" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>21</v>
       </c>
-      <c r="B30" s="81" t="s">
+      <c r="B30" s="75" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="79" t="s">
-        <v>206</v>
-      </c>
-      <c r="D30" s="79" t="s">
+      <c r="C30" s="73" t="s">
+        <v>203</v>
+      </c>
+      <c r="D30" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E30" s="80">
+      <c r="E30" s="74">
         <v>39794</v>
       </c>
-      <c r="F30" s="81" t="s">
-        <v>207</v>
-      </c>
-      <c r="G30" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="82">
+      <c r="F30" s="75" t="s">
+        <v>204</v>
+      </c>
+      <c r="G30" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="76">
         <v>75</v>
       </c>
-      <c r="I30" s="82">
+      <c r="I30" s="76">
         <v>43</v>
       </c>
-      <c r="J30" s="82">
+      <c r="J30" s="76">
         <f t="shared" si="0"/>
         <v>118</v>
       </c>
-      <c r="K30" s="82">
+      <c r="K30" s="76">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="L30" s="81" t="str">
+      <c r="L30" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M30" s="83" t="s">
-        <v>204</v>
+      <c r="M30" s="77" t="s">
+        <v>201</v>
       </c>
       <c r="N30"/>
     </row>
-    <row r="31" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="78">
+    <row r="31" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>22</v>
       </c>
-      <c r="B31" s="79" t="s">
+      <c r="B31" s="73" t="s">
         <v>120</v>
       </c>
-      <c r="C31" s="79" t="s">
+      <c r="C31" s="73" t="s">
         <v>121</v>
       </c>
-      <c r="D31" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="80">
+      <c r="D31" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="74">
         <v>39795</v>
       </c>
-      <c r="F31" s="81" t="s">
+      <c r="F31" s="75" t="s">
         <v>122</v>
       </c>
-      <c r="G31" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="85">
+      <c r="G31" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="79">
         <v>55</v>
       </c>
-      <c r="I31" s="82">
+      <c r="I31" s="76">
         <v>49</v>
       </c>
-      <c r="J31" s="82">
+      <c r="J31" s="76">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
-      <c r="K31" s="82">
+      <c r="K31" s="76">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="L31" s="81" t="str">
+      <c r="L31" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M31" s="83"/>
+      <c r="M31" s="77"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="78">
+    <row r="32" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>23</v>
       </c>
-      <c r="B32" s="79" t="s">
+      <c r="B32" s="73" t="s">
         <v>92</v>
       </c>
-      <c r="C32" s="79" t="s">
+      <c r="C32" s="73" t="s">
         <v>93</v>
       </c>
-      <c r="D32" s="79" t="s">
+      <c r="D32" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="80">
+      <c r="E32" s="74">
         <v>39575</v>
       </c>
-      <c r="F32" s="81" t="s">
+      <c r="F32" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="G32" s="87" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" s="88">
+      <c r="G32" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="82">
         <v>65</v>
       </c>
-      <c r="I32" s="82">
+      <c r="I32" s="76">
         <v>28</v>
       </c>
-      <c r="J32" s="82">
+      <c r="J32" s="76">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="K32" s="82">
+      <c r="K32" s="76">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="L32" s="81" t="str">
+      <c r="L32" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ធ្លាក់</v>
       </c>
-      <c r="M32" s="83"/>
+      <c r="M32" s="77"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="78">
+    <row r="33" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>24</v>
       </c>
-      <c r="B33" s="79" t="s">
+      <c r="B33" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="79" t="s">
+      <c r="C33" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="80">
+      <c r="D33" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="74">
         <v>39027</v>
       </c>
-      <c r="F33" s="81" t="s">
+      <c r="F33" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="G33" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="82">
+      <c r="G33" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="76">
         <v>45</v>
       </c>
-      <c r="I33" s="82">
+      <c r="I33" s="76">
         <v>66</v>
       </c>
-      <c r="J33" s="82">
+      <c r="J33" s="76">
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
-      <c r="K33" s="82">
+      <c r="K33" s="76">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="L33" s="81" t="str">
+      <c r="L33" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M33" s="83"/>
+      <c r="M33" s="77"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="78">
+    <row r="34" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>25</v>
       </c>
-      <c r="B34" s="79" t="s">
+      <c r="B34" s="73" t="s">
         <v>126</v>
       </c>
-      <c r="C34" s="79" t="s">
+      <c r="C34" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="D34" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="80">
+      <c r="D34" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="74">
         <v>39719</v>
       </c>
-      <c r="F34" s="84" t="s">
+      <c r="F34" s="78" t="s">
         <v>127</v>
       </c>
-      <c r="G34" s="84" t="s">
-        <v>20</v>
-      </c>
-      <c r="H34" s="82">
+      <c r="G34" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="76">
         <v>60</v>
       </c>
-      <c r="I34" s="82">
+      <c r="I34" s="76">
         <v>53</v>
       </c>
-      <c r="J34" s="82">
+      <c r="J34" s="76">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
-      <c r="K34" s="82">
+      <c r="K34" s="76">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="L34" s="81" t="str">
+      <c r="L34" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M34" s="83"/>
+      <c r="M34" s="77"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="78">
+    <row r="35" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>26</v>
       </c>
-      <c r="B35" s="79" t="s">
+      <c r="B35" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="79" t="s">
+      <c r="C35" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" s="80">
+      <c r="D35" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="74">
         <v>40102</v>
       </c>
-      <c r="F35" s="81" t="s">
-        <v>208</v>
-      </c>
-      <c r="G35" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H35" s="82">
+      <c r="F35" s="75" t="s">
+        <v>205</v>
+      </c>
+      <c r="G35" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="76">
         <v>60</v>
       </c>
-      <c r="I35" s="82">
+      <c r="I35" s="76">
         <v>31</v>
       </c>
-      <c r="J35" s="82">
+      <c r="J35" s="76">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="K35" s="82">
+      <c r="K35" s="76">
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="L35" s="81" t="str">
+      <c r="L35" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ធ្លាក់</v>
       </c>
-      <c r="M35" s="83" t="s">
+      <c r="M35" s="77" t="s">
         <v>42</v>
       </c>
       <c r="N35"/>
     </row>
-    <row r="36" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="78">
+    <row r="36" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>27</v>
       </c>
-      <c r="B36" s="79" t="s">
+      <c r="B36" s="73" t="s">
         <v>114</v>
       </c>
-      <c r="C36" s="79" t="s">
+      <c r="C36" s="73" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" s="80">
+      <c r="D36" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="74">
         <v>38862</v>
       </c>
-      <c r="F36" s="81" t="s">
+      <c r="F36" s="75" t="s">
         <v>116</v>
       </c>
-      <c r="G36" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H36" s="82">
+      <c r="G36" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="76">
         <v>65</v>
       </c>
-      <c r="I36" s="82">
+      <c r="I36" s="76">
         <v>43</v>
       </c>
-      <c r="J36" s="82">
+      <c r="J36" s="76">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
-      <c r="K36" s="82">
+      <c r="K36" s="76">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="L36" s="81" t="str">
+      <c r="L36" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M36" s="83"/>
+      <c r="M36" s="77"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="78">
+    <row r="37" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="72">
         <f t="shared" ca="1" si="3"/>
         <v>28</v>
       </c>
-      <c r="B37" s="79" t="s">
+      <c r="B37" s="73" t="s">
         <v>98</v>
       </c>
-      <c r="C37" s="79" t="s">
+      <c r="C37" s="73" t="s">
         <v>99</v>
       </c>
-      <c r="D37" s="79" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="80">
+      <c r="D37" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="74">
         <v>40437</v>
       </c>
-      <c r="F37" s="81" t="s">
+      <c r="F37" s="75" t="s">
         <v>100</v>
       </c>
-      <c r="G37" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="H37" s="82">
+      <c r="G37" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="76">
         <v>70</v>
       </c>
-      <c r="I37" s="82">
+      <c r="I37" s="76">
         <v>45</v>
       </c>
-      <c r="J37" s="82">
+      <c r="J37" s="76">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-      <c r="K37" s="82">
+      <c r="K37" s="76">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="L37" s="81" t="str">
+      <c r="L37" s="75" t="str">
         <f t="shared" si="2"/>
         <v>ជាប់</v>
       </c>
-      <c r="M37" s="83" t="s">
-        <v>204</v>
+      <c r="M37" s="77" t="s">
+        <v>201</v>
       </c>
       <c r="N37"/>
     </row>
-    <row r="38" spans="1:14" s="77" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" s="71" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19">
         <f t="shared" ca="1" si="3"/>
         <v>29</v>
@@ -7576,10 +6236,10 @@
         <v>36</v>
       </c>
       <c r="B45" s="52" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C45" s="52" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D45" s="52" t="s">
         <v>23</v>
@@ -7588,7 +6248,7 @@
         <v>39970</v>
       </c>
       <c r="F45" s="54" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G45" s="54" t="s">
         <v>20</v>
@@ -7612,7 +6272,7 @@
         <v>ជាប់</v>
       </c>
       <c r="M45" s="56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7633,7 +6293,7 @@
         <v>40071</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G46" s="22" t="s">
         <v>20</v>
@@ -7924,10 +6584,10 @@
         <v>44</v>
       </c>
       <c r="B53" s="52" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C53" s="52" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D53" s="52" t="s">
         <v>23</v>
@@ -7936,7 +6596,7 @@
         <v>39587</v>
       </c>
       <c r="F53" s="54" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G53" s="54" t="s">
         <v>20</v>
@@ -7960,7 +6620,7 @@
         <v>ជាប់</v>
       </c>
       <c r="M53" s="56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7978,7 +6638,7 @@
         <v>23</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F54" s="22" t="s">
         <v>109</v>
@@ -8012,10 +6672,10 @@
         <v>46</v>
       </c>
       <c r="B55" s="52" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C55" s="52" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D55" s="52" t="s">
         <v>23</v>
@@ -8024,7 +6684,7 @@
         <v>38781</v>
       </c>
       <c r="F55" s="54" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G55" s="54" t="s">
         <v>20</v>
@@ -8048,7 +6708,7 @@
         <v>ជាប់</v>
       </c>
       <c r="M55" s="56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8060,7 +6720,7 @@
         <v>62</v>
       </c>
       <c r="C56" s="52" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D56" s="52" t="s">
         <v>18</v>
@@ -8093,7 +6753,7 @@
         <v>ជាប់</v>
       </c>
       <c r="M56" s="56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8202,7 +6862,7 @@
         <v>39908</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G59" s="22" t="s">
         <v>20</v>
@@ -8362,10 +7022,10 @@
         <v>54</v>
       </c>
       <c r="B63" s="52" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C63" s="52" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D63" s="52" t="s">
         <v>23</v>
@@ -8374,7 +7034,7 @@
         <v>40037</v>
       </c>
       <c r="F63" s="54" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G63" s="54" t="s">
         <v>20</v>
@@ -8398,7 +7058,7 @@
         <v>ជាប់</v>
       </c>
       <c r="M63" s="56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8508,7 +7168,7 @@
         <v>41</v>
       </c>
       <c r="G66" s="22" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H66" s="23">
         <v>90</v>
@@ -8553,7 +7213,7 @@
         <v>41</v>
       </c>
       <c r="G67" s="22" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H67" s="23">
         <v>90</v>
@@ -8598,7 +7258,7 @@
         <v>19</v>
       </c>
       <c r="G68" s="22" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H68" s="23">
         <v>70</v>
@@ -8641,7 +7301,7 @@
         <v>41</v>
       </c>
       <c r="G69" s="22" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H69" s="23">
         <v>70</v>
@@ -8686,7 +7346,7 @@
         <v>41</v>
       </c>
       <c r="G70" s="22" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H70" s="23">
         <v>75</v>
@@ -8719,7 +7379,7 @@
         <v>167</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D71" s="20" t="s">
         <v>18</v>
@@ -8802,10 +7462,10 @@
         <v>64</v>
       </c>
       <c r="B73" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C73" s="52" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D73" s="52" t="s">
         <v>18</v>
@@ -8814,7 +7474,7 @@
         <v>38762</v>
       </c>
       <c r="F73" s="54" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G73" s="54" t="s">
         <v>141</v>
@@ -8838,7 +7498,7 @@
         <v>ជាប់</v>
       </c>
       <c r="M73" s="56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9111,10 +7771,10 @@
         <v>71</v>
       </c>
       <c r="B80" s="52" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C80" s="52" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D80" s="52" t="s">
         <v>18</v>
@@ -9123,7 +7783,7 @@
         <v>40030</v>
       </c>
       <c r="F80" s="52" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G80" s="52" t="s">
         <v>141</v>
@@ -9147,7 +7807,7 @@
         <v>ជាប់</v>
       </c>
       <c r="M80" s="56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="81" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9237,7 +7897,7 @@
         <v>ជាប់</v>
       </c>
       <c r="M82" s="56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="83" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9246,10 +7906,10 @@
         <v>74</v>
       </c>
       <c r="B83" s="52" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C83" s="52" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D83" s="52" t="s">
         <v>18</v>
@@ -9258,7 +7918,7 @@
         <v>39824</v>
       </c>
       <c r="F83" s="54" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G83" s="54" t="s">
         <v>141</v>
@@ -9282,7 +7942,7 @@
         <v>ជាប់</v>
       </c>
       <c r="M83" s="56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="84" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
